--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.32334462450737</v>
+        <v>6.715043501482448</v>
       </c>
       <c r="D2" t="n">
-        <v>39.72334988523436</v>
+        <v>6.455044356350585</v>
       </c>
       <c r="E2" t="n">
-        <v>8.164182880049124</v>
+        <v>1.326679718007983</v>
       </c>
       <c r="F2" t="n">
-        <v>8.966208217618314</v>
+        <v>1.457008835362976</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.15379126114147</v>
+        <v>8.149991079935489</v>
       </c>
       <c r="D3" t="n">
-        <v>48.57773454896157</v>
+        <v>7.893881864206254</v>
       </c>
       <c r="E3" t="n">
-        <v>8.164182880049124</v>
+        <v>1.326679718007983</v>
       </c>
       <c r="F3" t="n">
-        <v>8.966208217618314</v>
+        <v>1.457008835362976</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.29192748285168</v>
+        <v>8.984938215963398</v>
       </c>
       <c r="D4" t="n">
-        <v>54.89959062340512</v>
+        <v>8.921183476303332</v>
       </c>
       <c r="E4" t="n">
-        <v>8.164182880049124</v>
+        <v>1.326679718007983</v>
       </c>
       <c r="F4" t="n">
-        <v>8.966208217618314</v>
+        <v>1.457008835362976</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.83532844085364</v>
+        <v>10.37324087163872</v>
       </c>
       <c r="D5" t="n">
-        <v>64.2801981950864</v>
+        <v>10.44553220670154</v>
       </c>
       <c r="E5" t="n">
-        <v>8.164182880049124</v>
+        <v>1.326679718007983</v>
       </c>
       <c r="F5" t="n">
-        <v>8.966208217618314</v>
+        <v>1.457008835362976</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
